--- a/dev/StructureDefinition-ereferral-provenance.xlsx
+++ b/dev/StructureDefinition-ereferral-provenance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T22:56:55+00:00</t>
+    <t>2026-06-16T23:15:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ereferral-provenance.xlsx
+++ b/dev/StructureDefinition-ereferral-provenance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T23:15:28+00:00</t>
+    <t>2026-06-16T23:27:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ereferral-provenance.xlsx
+++ b/dev/StructureDefinition-ereferral-provenance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T23:27:01+00:00</t>
+    <t>2026-06-17T00:00:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ereferral-provenance.xlsx
+++ b/dev/StructureDefinition-ereferral-provenance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T00:00:17+00:00</t>
+    <t>2026-06-17T00:17:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ereferral-provenance.xlsx
+++ b/dev/StructureDefinition-ereferral-provenance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T00:17:01+00:00</t>
+    <t>2026-06-17T00:28:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ereferral-provenance.xlsx
+++ b/dev/StructureDefinition-ereferral-provenance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T00:28:17+00:00</t>
+    <t>2026-06-17T00:35:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ereferral-provenance.xlsx
+++ b/dev/StructureDefinition-ereferral-provenance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T00:35:38+00:00</t>
+    <t>2026-06-17T04:31:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ereferral-provenance.xlsx
+++ b/dev/StructureDefinition-ereferral-provenance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T04:31:39+00:00</t>
+    <t>2026-06-17T05:47:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ereferral-provenance.xlsx
+++ b/dev/StructureDefinition-ereferral-provenance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T05:47:03+00:00</t>
+    <t>2026-06-17T10:39:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -491,7 +491,7 @@
     <t>The Reference(s) that were generated or updated by the activity described in this resource. A provenance can point to more than one target if multiple resources were created/updated by a single activity.</t>
   </si>
   <si>
-    <t>See the [PH Core Provenance Profile](https://build.fhir.org/ig/jgsuess/ph-core/StructureDefinition-ph-core-provenance.html) for guidance on supported resource types.</t>
+    <t>See the [PH Core Provenance Profile](file:///home/runner/work/ph-core/ph-core/output/StructureDefinition-ph-core-provenance.html) for guidance on supported resource types.</t>
   </si>
   <si>
     <t>./outboundRelationship[isNormalActRelationship() and typeCode=SUBJ]/target  OR  ./participation[isNormalParticipation() and typeCode=SBJ]/role  OR  ./participation[isNormalParticipation() and typeCode=SBJ]/role[isNormalRole()]/player</t>

--- a/dev/StructureDefinition-ereferral-provenance.xlsx
+++ b/dev/StructureDefinition-ereferral-provenance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T10:39:22+00:00</t>
+    <t>2026-06-17T12:31:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ereferral-provenance.xlsx
+++ b/dev/StructureDefinition-ereferral-provenance.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T12:31:02+00:00</t>
+    <t>2026-07-07T09:49:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
